--- a/artfynd/A 53502-2025 artfynd.xlsx
+++ b/artfynd/A 53502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000496</v>
       </c>
       <c r="B2" t="n">
-        <v>104175</v>
+        <v>104179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53502-2025 artfynd.xlsx
+++ b/artfynd/A 53502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000496</v>
       </c>
       <c r="B2" t="n">
-        <v>104179</v>
+        <v>104181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53502-2025 artfynd.xlsx
+++ b/artfynd/A 53502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000496</v>
       </c>
       <c r="B2" t="n">
-        <v>104181</v>
+        <v>104185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53502-2025 artfynd.xlsx
+++ b/artfynd/A 53502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000496</v>
       </c>
       <c r="B2" t="n">
-        <v>104185</v>
+        <v>104195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53502-2025 artfynd.xlsx
+++ b/artfynd/A 53502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000496</v>
       </c>
       <c r="B2" t="n">
-        <v>104195</v>
+        <v>104198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53502-2025 artfynd.xlsx
+++ b/artfynd/A 53502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000496</v>
       </c>
       <c r="B2" t="n">
-        <v>104198</v>
+        <v>104627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
